--- a/artfynd/A 14672-2026 artfynd.xlsx
+++ b/artfynd/A 14672-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AY47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132747788</v>
+        <v>132747774</v>
       </c>
       <c r="B2" t="n">
-        <v>79333</v>
+        <v>79373</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>542413</v>
+        <v>542401</v>
       </c>
       <c r="R2" t="n">
-        <v>6983076</v>
+        <v>6983005</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,11 +749,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,14 +796,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132747794</v>
+        <v>132747775</v>
       </c>
       <c r="B3" t="n">
-        <v>79333</v>
+        <v>79373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -839,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>542525</v>
+        <v>542422</v>
       </c>
       <c r="R3" t="n">
-        <v>6983005</v>
+        <v>6983044</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -927,32 +922,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132747765</v>
+        <v>132747776</v>
       </c>
       <c r="B4" t="n">
-        <v>80466</v>
+        <v>79373</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -965,10 +960,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>542405</v>
+        <v>542406</v>
       </c>
       <c r="R4" t="n">
-        <v>6983064</v>
+        <v>6983024</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1016,6 +1011,21 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1033,14 +1043,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132747792</v>
+        <v>132747777</v>
       </c>
       <c r="B5" t="n">
-        <v>79333</v>
+        <v>79373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1071,10 +1081,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>542441</v>
+        <v>542383</v>
       </c>
       <c r="R5" t="n">
-        <v>6983057</v>
+        <v>6983011</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1154,14 +1164,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132747793</v>
+        <v>132747779</v>
       </c>
       <c r="B6" t="n">
-        <v>79333</v>
+        <v>79373</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1192,10 +1202,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>542522</v>
+        <v>542355</v>
       </c>
       <c r="R6" t="n">
-        <v>6983026</v>
+        <v>6983055</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,6 +1240,11 @@
           <t>2026-04-21</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Garnlav på grenar av en stående död gran med sannolika födosökspår efter tretåig hackspett.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1242,7 +1257,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1255,9 +1270,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1275,38 +1295,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132747762</v>
+        <v>132747780</v>
       </c>
       <c r="B7" t="n">
-        <v>97995</v>
+        <v>79373</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1314,10 +1333,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>542369</v>
+        <v>542317</v>
       </c>
       <c r="R7" t="n">
-        <v>6983040</v>
+        <v>6983006</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1365,6 +1384,21 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1382,14 +1416,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132747789</v>
+        <v>132747782</v>
       </c>
       <c r="B8" t="n">
-        <v>79333</v>
+        <v>79373</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1420,10 +1454,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>542428</v>
+        <v>542293</v>
       </c>
       <c r="R8" t="n">
-        <v>6983043</v>
+        <v>6983030</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1458,6 +1492,11 @@
           <t>2026-04-21</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1470,7 +1509,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1503,41 +1542,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132747767</v>
+        <v>132747783</v>
       </c>
       <c r="B9" t="n">
-        <v>80438</v>
+        <v>79373</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1545,10 +1580,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>542326</v>
+        <v>542297</v>
       </c>
       <c r="R9" t="n">
-        <v>6983006</v>
+        <v>6983062</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1595,27 +1630,27 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1633,10 +1668,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132747772</v>
+        <v>132747784</v>
       </c>
       <c r="B10" t="n">
-        <v>99130</v>
+        <v>79373</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1644,54 +1679,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Nedre Lillmyran, Finnsjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>542527</v>
+        <v>542321</v>
       </c>
       <c r="R10" t="n">
-        <v>6983004</v>
+        <v>6983113</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1728,7 +1746,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Minst 21 plantor och 3 vinterståndare inom ca 1,5 m2 yta i gles granskog nära en mindre bäck.</t>
+          <t>På barken av flera tallar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1743,7 +1761,27 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1761,14 +1799,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132747777</v>
+        <v>132747785</v>
       </c>
       <c r="B11" t="n">
-        <v>79333</v>
+        <v>79373</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1799,10 +1837,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>542383</v>
+        <v>542392</v>
       </c>
       <c r="R11" t="n">
-        <v>6983011</v>
+        <v>6983097</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1837,6 +1875,11 @@
           <t>2026-04-21</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rikligt på flera granar.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1862,9 +1905,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1882,10 +1930,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132747771</v>
+        <v>132747786</v>
       </c>
       <c r="B12" t="n">
-        <v>99130</v>
+        <v>79373</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1893,54 +1941,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Nedre Lillmyran, Finnsjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>542502</v>
+        <v>542385</v>
       </c>
       <c r="R12" t="n">
-        <v>6983031</v>
+        <v>6983049</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1977,7 +2008,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Minst 30 plantor inom ca 1 m2 yta.</t>
+          <t>På flera både döda och levande granar.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1995,9 +2026,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Gles granskog vid gräns mot tallskog.</t>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2015,41 +2061,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132747766</v>
+        <v>132747787</v>
       </c>
       <c r="B13" t="n">
-        <v>80438</v>
+        <v>79373</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2057,10 +2099,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>542334</v>
+        <v>542396</v>
       </c>
       <c r="R13" t="n">
-        <v>6983023</v>
+        <v>6983061</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2097,7 +2139,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Fertil lunglav med apothecier på en sälg.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2117,22 +2159,17 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2150,14 +2187,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132747787</v>
+        <v>132747788</v>
       </c>
       <c r="B14" t="n">
-        <v>79333</v>
+        <v>79373</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2188,10 +2225,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>542396</v>
+        <v>542413</v>
       </c>
       <c r="R14" t="n">
-        <v>6983061</v>
+        <v>6983076</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2276,14 +2313,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132747774</v>
+        <v>132747789</v>
       </c>
       <c r="B15" t="n">
-        <v>79333</v>
+        <v>79373</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2314,10 +2351,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>542401</v>
+        <v>542428</v>
       </c>
       <c r="R15" t="n">
-        <v>6983005</v>
+        <v>6983043</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2397,14 +2434,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132747779</v>
+        <v>132747791</v>
       </c>
       <c r="B16" t="n">
-        <v>79333</v>
+        <v>79373</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2435,10 +2472,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>542355</v>
+        <v>542435</v>
       </c>
       <c r="R16" t="n">
-        <v>6983055</v>
+        <v>6983033</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2473,11 +2510,6 @@
           <t>2026-04-21</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Garnlav på grenar av en stående död gran med sannolika födosökspår efter tretåig hackspett.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2490,7 +2522,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -2503,14 +2535,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2528,14 +2555,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132747776</v>
+        <v>132747792</v>
       </c>
       <c r="B17" t="n">
-        <v>79333</v>
+        <v>79373</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2566,10 +2593,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>542406</v>
+        <v>542441</v>
       </c>
       <c r="R17" t="n">
-        <v>6983024</v>
+        <v>6983057</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2649,14 +2676,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132747775</v>
+        <v>132747793</v>
       </c>
       <c r="B18" t="n">
-        <v>79333</v>
+        <v>79373</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2687,10 +2714,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>542422</v>
+        <v>542522</v>
       </c>
       <c r="R18" t="n">
-        <v>6983044</v>
+        <v>6983026</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2723,11 +2750,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2775,14 +2797,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132747780</v>
+        <v>132747794</v>
       </c>
       <c r="B19" t="n">
-        <v>79333</v>
+        <v>79373</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2813,10 +2835,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>542317</v>
+        <v>542525</v>
       </c>
       <c r="R19" t="n">
-        <v>6983006</v>
+        <v>6983005</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2849,6 +2871,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2896,37 +2923,41 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132747764</v>
+        <v>132747766</v>
       </c>
       <c r="B20" t="n">
-        <v>80466</v>
+        <v>80488</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2934,10 +2965,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>542366</v>
+        <v>542334</v>
       </c>
       <c r="R20" t="n">
-        <v>6983107</v>
+        <v>6983023</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2972,6 +3003,11 @@
           <t>2026-04-21</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Fertil lunglav med apothecier på en sälg.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2984,7 +3020,27 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3002,10 +3058,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132747783</v>
+        <v>132747767</v>
       </c>
       <c r="B21" t="n">
-        <v>79333</v>
+        <v>80488</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3013,26 +3069,30 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3040,10 +3100,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>542297</v>
+        <v>542326</v>
       </c>
       <c r="R21" t="n">
-        <v>6983062</v>
+        <v>6983006</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3090,27 +3150,27 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3131,7 +3191,7 @@
         <v>132747763</v>
       </c>
       <c r="B22" t="n">
-        <v>80466</v>
+        <v>80492</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3239,32 +3299,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132747785</v>
+        <v>132747764</v>
       </c>
       <c r="B23" t="n">
-        <v>79333</v>
+        <v>80492</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3277,10 +3337,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>542392</v>
+        <v>542366</v>
       </c>
       <c r="R23" t="n">
-        <v>6983097</v>
+        <v>6983107</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3315,11 +3375,6 @@
           <t>2026-04-21</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Rikligt på flera granar.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3332,27 +3387,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3370,32 +3405,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132747782</v>
+        <v>132747765</v>
       </c>
       <c r="B24" t="n">
-        <v>79333</v>
+        <v>80492</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3408,10 +3443,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>542293</v>
+        <v>542405</v>
       </c>
       <c r="R24" t="n">
-        <v>6983030</v>
+        <v>6983064</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3446,11 +3481,6 @@
           <t>2026-04-21</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3463,22 +3493,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3496,10 +3511,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132747786</v>
+        <v>132747747</v>
       </c>
       <c r="B25" t="n">
-        <v>79333</v>
+        <v>57975</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3507,26 +3522,31 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3534,10 +3554,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>542385</v>
+        <v>542426</v>
       </c>
       <c r="R25" t="n">
-        <v>6983049</v>
+        <v>6983060</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3574,7 +3594,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På flera både döda och levande granar.</t>
+          <t>Ringhack, äldre, längs flera meter på en gran.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3583,7 +3603,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3602,14 +3621,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3627,10 +3641,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132747784</v>
+        <v>132747748</v>
       </c>
       <c r="B26" t="n">
-        <v>79333</v>
+        <v>57975</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3638,26 +3652,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3665,10 +3684,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>542321</v>
+        <v>542312</v>
       </c>
       <c r="R26" t="n">
-        <v>6983113</v>
+        <v>6982991</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3705,7 +3724,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På barken av flera tallar.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3714,33 +3733,37 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>På fuktig mark.</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3758,7 +3781,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132747755</v>
+        <v>132747749</v>
       </c>
       <c r="B27" t="n">
         <v>57975</v>
@@ -3801,10 +3824,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>542294</v>
+        <v>542302</v>
       </c>
       <c r="R27" t="n">
-        <v>6983054</v>
+        <v>6982977</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3841,7 +3864,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en smal gran.</t>
+          <t>Ringhack, färska, högt upp på en gran.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3893,7 +3916,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132747747</v>
+        <v>132747750</v>
       </c>
       <c r="B28" t="n">
         <v>57975</v>
@@ -3926,7 +3949,7 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -3936,10 +3959,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>542426</v>
+        <v>542297</v>
       </c>
       <c r="R28" t="n">
-        <v>6983060</v>
+        <v>6982973</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3976,7 +3999,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs flera meter på en gran.</t>
+          <t>Ringhack, färska, högt upp på en gran.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3990,7 +4013,7 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
@@ -4003,9 +4026,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4023,7 +4051,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132747758</v>
+        <v>132747751</v>
       </c>
       <c r="B29" t="n">
         <v>57975</v>
@@ -4056,7 +4084,7 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -4066,10 +4094,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>542299</v>
+        <v>542290</v>
       </c>
       <c r="R29" t="n">
-        <v>6983102</v>
+        <v>6983025</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4106,7 +4134,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, högt upp på en tall.</t>
+          <t>Ringhack (savhack), färska, på en gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4120,17 +4148,17 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
@@ -4140,7 +4168,7 @@
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4293,7 +4321,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132747759</v>
+        <v>132747753</v>
       </c>
       <c r="B31" t="n">
         <v>57975</v>
@@ -4336,10 +4364,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>542303</v>
+        <v>542286</v>
       </c>
       <c r="R31" t="n">
-        <v>6983106</v>
+        <v>6983042</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4376,7 +4404,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, högt upp på en tall i tallskog.</t>
+          <t>Ringhack (savhack), färska, på en gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4390,17 +4418,17 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
@@ -4410,7 +4438,7 @@
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4428,7 +4456,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132747753</v>
+        <v>132747754</v>
       </c>
       <c r="B32" t="n">
         <v>57975</v>
@@ -4471,10 +4499,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>542286</v>
+        <v>542292</v>
       </c>
       <c r="R32" t="n">
-        <v>6983042</v>
+        <v>6983049</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4563,7 +4591,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132747754</v>
+        <v>132747755</v>
       </c>
       <c r="B33" t="n">
         <v>57975</v>
@@ -4606,10 +4634,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>542292</v>
+        <v>542294</v>
       </c>
       <c r="R33" t="n">
-        <v>6983049</v>
+        <v>6983054</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4646,7 +4674,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran.</t>
+          <t>Ringhack, färska, på en smal gran.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4833,7 +4861,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132747751</v>
+        <v>132747757</v>
       </c>
       <c r="B35" t="n">
         <v>57975</v>
@@ -4866,7 +4894,7 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -4876,10 +4904,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>542290</v>
+        <v>542299</v>
       </c>
       <c r="R35" t="n">
-        <v>6983025</v>
+        <v>6983093</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4916,7 +4944,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran.</t>
+          <t>Ringhack, äldre, högt upp på en tall.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4930,17 +4958,17 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
@@ -4950,7 +4978,7 @@
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4968,7 +4996,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132747761</v>
+        <v>132747758</v>
       </c>
       <c r="B36" t="n">
         <v>57975</v>
@@ -5011,10 +5039,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>542390</v>
+        <v>542299</v>
       </c>
       <c r="R36" t="n">
-        <v>6983081</v>
+        <v>6983102</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5051,7 +5079,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>Ringhack, äldre, högt upp på en tall.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5065,22 +5093,27 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5098,7 +5131,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132747757</v>
+        <v>132747759</v>
       </c>
       <c r="B37" t="n">
         <v>57975</v>
@@ -5131,7 +5164,7 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -5141,10 +5174,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>542299</v>
+        <v>542303</v>
       </c>
       <c r="R37" t="n">
-        <v>6983093</v>
+        <v>6983106</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5181,7 +5214,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, högt upp på en tall.</t>
+          <t>Ringhack, färska och äldre, högt upp på en tall i tallskog.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5368,7 +5401,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132747748</v>
+        <v>132747761</v>
       </c>
       <c r="B39" t="n">
         <v>57975</v>
@@ -5401,7 +5434,7 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -5411,10 +5444,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>542312</v>
+        <v>542390</v>
       </c>
       <c r="R39" t="n">
-        <v>6982991</v>
+        <v>6983081</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5451,7 +5484,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5465,12 +5498,7 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>På fuktig mark.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ39" t="inlineStr">
@@ -5483,14 +5511,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5505,6 +5528,924 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>132747768</v>
+      </c>
+      <c r="B40" t="n">
+        <v>111153</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Nedre Lillmyran, Finnsjöberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>542337</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6983052</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>132747769</v>
+      </c>
+      <c r="B41" t="n">
+        <v>111153</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Nedre Lillmyran, Finnsjöberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>542433</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6983063</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>132747770</v>
+      </c>
+      <c r="B42" t="n">
+        <v>111153</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Nedre Lillmyran, Finnsjöberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>542525</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6982999</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>132747771</v>
+      </c>
+      <c r="B43" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Nedre Lillmyran, Finnsjöberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>542502</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6983031</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Minst 30 plantor inom ca 1 m2 yta.</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>Gles granskog vid gräns mot tallskog.</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>132747772</v>
+      </c>
+      <c r="B44" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Nedre Lillmyran, Finnsjöberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>542527</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6983004</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Minst 21 plantor och 3 vinterståndare inom ca 1,5 m2 yta i gles granskog nära en mindre bäck.</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>132747762</v>
+      </c>
+      <c r="B45" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Nedre Lillmyran, Finnsjöberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>542369</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6983040</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>132747795</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79057</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>228659</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Fönsterlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Cladonia stellaris</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Opiz) Pouzar &amp; Vezda</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Nedre Lillmyran, Finnsjöberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>542304</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6983083</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>Gles tallskog.</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>132747796</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79057</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>228659</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Fönsterlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Cladonia stellaris</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Opiz) Pouzar &amp; Vezda</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Nedre Lillmyran, Finnsjöberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>542324</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6983111</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14672-2026 artfynd.xlsx
+++ b/artfynd/A 14672-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY47"/>
+  <dimension ref="A1:AZ47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132747774</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -919,6 +929,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132747775</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1040,6 +1055,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132747776</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1161,6 +1181,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132747777</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1292,6 +1317,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132747779</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1413,6 +1443,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132747780</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1539,6 +1574,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132747782</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1665,6 +1705,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132747783</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1796,6 +1841,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132747784</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1927,6 +1977,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132747785</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2058,6 +2113,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132747786</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2184,6 +2244,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132747787</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2310,6 +2375,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132747788</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2431,6 +2501,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132747789</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2552,6 +2627,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132747791</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2673,6 +2753,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132747792</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2794,6 +2879,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132747793</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2920,6 +3010,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132747794</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3055,6 +3150,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132747766</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3185,6 +3285,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132747767</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3296,6 +3401,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132747763</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3402,6 +3512,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132747764</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3508,6 +3623,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132747765</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3638,6 +3758,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132747747</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3778,6 +3903,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132747748</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3913,6 +4043,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132747749</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4048,6 +4183,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132747750</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4183,6 +4323,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132747751</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4318,6 +4463,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132747752</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4453,6 +4603,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132747753</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4588,6 +4743,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132747754</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4723,6 +4883,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132747755</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4858,6 +5023,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132747756</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4993,6 +5163,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132747757</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -5128,6 +5303,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132747758</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5263,6 +5443,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132747759</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5398,6 +5583,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132747760</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5528,6 +5718,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132747761</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5639,6 +5834,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132747768</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5750,6 +5950,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132747769</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5861,6 +6066,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132747770</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5994,6 +6204,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132747771</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -6122,6 +6337,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132747772</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -6229,6 +6449,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132747762</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6340,6 +6565,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132747795</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6446,8 +6676,61 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132747796</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>